--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2695" uniqueCount="567">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2684" uniqueCount="556">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-14T12:31:04+00:00</t>
+    <t>2025-03-04T08:19:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -282,7 +282,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -338,17 +338,10 @@
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>Observation.implicitRules</t>
   </si>
   <si>
@@ -368,9 +361,6 @@
     <t>Resource.implicitRules</t>
   </si>
   <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Observation.language</t>
   </si>
   <si>
@@ -448,6 +438,9 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
+    <t>N/A</t>
+  </si>
+  <si>
     <t>Observation.extension</t>
   </si>
   <si>
@@ -468,16 +461,6 @@
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>DomainResource.extension</t>
   </si>
   <si>
@@ -546,14 +529,7 @@
     <t>A plan, proposal or order that is fulfilled in whole or in part by this event.  For example, a MedicationRequest may require a patient to have laboratory test performed before  it is dispensed.</t>
   </si>
   <si>
-    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
-  </si>
-  <si>
     <t>Allows tracing of authorization for the event and tracking whether proposals/recommendations were acted upon.</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
   </si>
   <si>
     <t>Event.basedOn</t>
@@ -656,9 +632,6 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/observation-category</t>
-  </si>
-  <si>
-    <t>CE/CNE/CWE</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
@@ -914,8 +887,8 @@
     <t>An observation exists to have a value, though it might not if it is in error, or if it represents a group of observations.</t>
   </si>
   <si>
-    <t>ele-1
-obs-7</t>
+    <t xml:space="preserve">obs-7
+</t>
   </si>
   <si>
     <t>&lt; 441742003 |Evaluation finding|</t>
@@ -946,10 +919,23 @@
     <t>Element.id</t>
   </si>
   <si>
+    <t>n/a</t>
+  </si>
+  <si>
     <t>Observation.value[x].extension</t>
   </si>
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
   </si>
   <si>
     <t>Element.extension</t>
@@ -992,9 +978,6 @@
     <t>How the value should be understood and represented - whether the actual value is greater or less than the stated value due to measurement issues; e.g. if the comparator is "&lt;" , then the real value is &lt; stated value.</t>
   </si>
   <si>
-    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
-  </si>
-  <si>
     <t>Need a framework for handling measures where the value is &lt;5ug/L or &gt;400mg/L due to the limitations of measuring methodology.</t>
   </si>
   <si>
@@ -1049,9 +1032,6 @@
     <t>The identification of the system that provides the coded form of the unit.</t>
   </si>
   <si>
-    <t>see http://en.wikipedia.org/wiki/Uniform_resource_identifier</t>
-  </si>
-  <si>
     <t>Need to know the system that defines the coded form of the unit.</t>
   </si>
   <si>
@@ -1061,8 +1041,8 @@
     <t>Quantity.system</t>
   </si>
   <si>
-    <t>ele-1
-qty-3</t>
+    <t xml:space="preserve">qty-3
+</t>
   </si>
   <si>
     <t>CO.codeSystem, PQ.translation.codeSystem</t>
@@ -1114,8 +1094,8 @@
     <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
   </si>
   <si>
-    <t>ele-1
-obs-6</t>
+    <t xml:space="preserve">obs-6
+</t>
   </si>
   <si>
     <t>value.nullFlavor</t>
@@ -1541,15 +1521,8 @@
     <t>The value of the low bound of the reference range.  The low bound of the reference range endpoint is inclusive of the value (e.g.  reference range is &gt;=5 - &lt;=9). If the low bound is omitted,  it is assumed to be meaningless (e.g. reference range is &lt;=2.3).</t>
   </si>
   <si>
-    <t>The context of use may frequently define what kind of quantity this is and therefore what kind of units can be used. The context of use may also restrict the values for the comparator.</t>
-  </si>
-  <si>
-    <t>ele-1
-obs-3</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-qty-3:If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
+    <t xml:space="preserve">obs-3
+</t>
   </si>
   <si>
     <t>OBX-7</t>
@@ -1637,17 +1610,7 @@
     <t>The age at which this reference range is applicable. This is a neonatal age (e.g. number of weeks at term) if the meaning says so.</t>
   </si>
   <si>
-    <t>The stated low and high value are assumed to have arbitrarily high precision when it comes to determining which values are in the range. I.e. 1.99 is not in the range 2 -&gt; 3.</t>
-  </si>
-  <si>
     <t>Some analytes vary greatly over age.</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-rng-2:If present, low SHALL have a lower value than high {low.empty() or high.empty() or (low &lt;= high)}</t>
-  </si>
-  <si>
-    <t>NR and also possibly SN (but see also quantity)</t>
   </si>
   <si>
     <t>outboundRelationship[typeCode=PRCN].targetObservationCriterion[code="age"].value</t>
@@ -2615,11 +2578,11 @@
         <v>93</v>
       </c>
       <c r="AI4" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ4" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ4" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK4" t="s" s="2">
         <v>82</v>
       </c>
@@ -2630,7 +2593,7 @@
         <v>82</v>
       </c>
       <c r="AN4" t="s" s="2">
-        <v>107</v>
+        <v>82</v>
       </c>
       <c r="AO4" t="s" s="2">
         <v>82</v>
@@ -2641,10 +2604,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2667,16 +2630,16 @@
         <v>94</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L5" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="M5" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="L5" t="s" s="2">
+      <c r="N5" t="s" s="2">
         <v>110</v>
-      </c>
-      <c r="M5" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>112</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2726,7 +2689,7 @@
         <v>82</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>80</v>
@@ -2735,11 +2698,11 @@
         <v>93</v>
       </c>
       <c r="AI5" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ5" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ5" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK5" t="s" s="2">
         <v>82</v>
       </c>
@@ -2750,7 +2713,7 @@
         <v>82</v>
       </c>
       <c r="AN5" t="s" s="2">
-        <v>114</v>
+        <v>82</v>
       </c>
       <c r="AO5" t="s" s="2">
         <v>82</v>
@@ -2761,10 +2724,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2787,16 +2750,16 @@
         <v>82</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="L6" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="M6" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="N6" t="s" s="2">
         <v>116</v>
-      </c>
-      <c r="L6" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="M6" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>119</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2822,31 +2785,31 @@
         <v>82</v>
       </c>
       <c r="X6" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="Y6" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="Z6" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AA6" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE6" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF6" t="s" s="2">
         <v>120</v>
-      </c>
-      <c r="Y6" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="Z6" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="AA6" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>123</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>80</v>
@@ -2855,11 +2818,11 @@
         <v>93</v>
       </c>
       <c r="AI6" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ6" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ6" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK6" t="s" s="2">
         <v>82</v>
       </c>
@@ -2870,7 +2833,7 @@
         <v>82</v>
       </c>
       <c r="AN6" t="s" s="2">
-        <v>114</v>
+        <v>82</v>
       </c>
       <c r="AO6" t="s" s="2">
         <v>82</v>
@@ -2881,14 +2844,14 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -2907,16 +2870,16 @@
         <v>82</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="L7" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="M7" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="N7" t="s" s="2">
         <v>126</v>
-      </c>
-      <c r="L7" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="M7" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>129</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2966,7 +2929,7 @@
         <v>82</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>80</v>
@@ -2975,11 +2938,11 @@
         <v>93</v>
       </c>
       <c r="AI7" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ7" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ7" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK7" t="s" s="2">
         <v>82</v>
       </c>
@@ -2990,7 +2953,7 @@
         <v>82</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="AO7" t="s" s="2">
         <v>82</v>
@@ -3001,14 +2964,14 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -3027,16 +2990,16 @@
         <v>82</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L8" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="M8" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="N8" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="L8" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="M8" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>137</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -3086,7 +3049,7 @@
         <v>82</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
@@ -3110,7 +3073,7 @@
         <v>82</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="AO8" t="s" s="2">
         <v>82</v>
@@ -3121,14 +3084,14 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -3147,16 +3110,16 @@
         <v>82</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L9" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="M9" t="s" s="2">
         <v>141</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="N9" t="s" s="2">
         <v>142</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>144</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -3194,19 +3157,19 @@
         <v>82</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>145</v>
+        <v>82</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>146</v>
+        <v>82</v>
       </c>
       <c r="AD9" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>147</v>
+        <v>82</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
@@ -3215,10 +3178,10 @@
         <v>81</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>82</v>
@@ -3230,7 +3193,7 @@
         <v>82</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="AO9" t="s" s="2">
         <v>82</v>
@@ -3241,14 +3204,14 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -3267,19 +3230,19 @@
         <v>82</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>82</v>
@@ -3316,19 +3279,19 @@
         <v>82</v>
       </c>
       <c r="AB10" t="s" s="2">
-        <v>145</v>
+        <v>82</v>
       </c>
       <c r="AC10" t="s" s="2">
-        <v>146</v>
+        <v>82</v>
       </c>
       <c r="AD10" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE10" t="s" s="2">
-        <v>147</v>
+        <v>82</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -3337,10 +3300,10 @@
         <v>81</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>82</v>
@@ -3352,7 +3315,7 @@
         <v>82</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="AO10" t="s" s="2">
         <v>82</v>
@@ -3363,10 +3326,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3389,17 +3352,17 @@
         <v>94</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" t="s" s="2">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>82</v>
@@ -3448,7 +3411,7 @@
         <v>82</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -3457,25 +3420,25 @@
         <v>81</v>
       </c>
       <c r="AI11" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ11" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ11" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK11" t="s" s="2">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="AP11" t="s" s="2">
         <v>82</v>
@@ -3483,14 +3446,14 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -3509,19 +3472,17 @@
         <v>94</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>169</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>82</v>
@@ -3570,7 +3531,7 @@
         <v>82</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -3579,22 +3540,22 @@
         <v>81</v>
       </c>
       <c r="AI12" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ12" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ12" t="s" s="2">
-        <v>171</v>
-      </c>
       <c r="AK12" t="s" s="2">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>82</v>
@@ -3605,14 +3566,14 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -3631,16 +3592,16 @@
         <v>94</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3690,7 +3651,7 @@
         <v>82</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -3699,22 +3660,22 @@
         <v>81</v>
       </c>
       <c r="AI13" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ13" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ13" t="s" s="2">
-        <v>171</v>
-      </c>
       <c r="AK13" t="s" s="2">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>82</v>
@@ -3725,10 +3686,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3751,19 +3712,19 @@
         <v>94</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>82</v>
@@ -3788,13 +3749,13 @@
         <v>82</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>82</v>
@@ -3812,7 +3773,7 @@
         <v>82</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>93</v>
@@ -3821,25 +3782,25 @@
         <v>93</v>
       </c>
       <c r="AI14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ14" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ14" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK14" t="s" s="2">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="AP14" t="s" s="2">
         <v>82</v>
@@ -3847,10 +3808,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3873,19 +3834,19 @@
         <v>82</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>82</v>
@@ -3910,13 +3871,13 @@
         <v>82</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>82</v>
@@ -3934,7 +3895,7 @@
         <v>82</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -3943,11 +3904,11 @@
         <v>81</v>
       </c>
       <c r="AI15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ15" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ15" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK15" t="s" s="2">
         <v>82</v>
       </c>
@@ -3955,13 +3916,13 @@
         <v>82</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>205</v>
+        <v>82</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>82</v>
@@ -3969,14 +3930,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3995,19 +3956,19 @@
         <v>94</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>82</v>
@@ -4017,7 +3978,7 @@
         <v>82</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>82</v>
@@ -4032,13 +3993,13 @@
         <v>82</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>82</v>
@@ -4056,7 +4017,7 @@
         <v>82</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>93</v>
@@ -4065,36 +4026,36 @@
         <v>93</v>
       </c>
       <c r="AI16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ16" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK16" t="s" s="2">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>223</v>
+        <v>215</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4117,19 +4078,19 @@
         <v>94</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>82</v>
@@ -4178,7 +4139,7 @@
         <v>82</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -4187,25 +4148,25 @@
         <v>93</v>
       </c>
       <c r="AI17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ17" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ17" t="s" s="2">
-        <v>171</v>
-      </c>
       <c r="AK17" t="s" s="2">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>82</v>
@@ -4213,10 +4174,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4239,16 +4200,16 @@
         <v>94</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4298,7 +4259,7 @@
         <v>82</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4307,11 +4268,11 @@
         <v>81</v>
       </c>
       <c r="AI18" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ18" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ18" t="s" s="2">
-        <v>171</v>
-      </c>
       <c r="AK18" t="s" s="2">
         <v>82</v>
       </c>
@@ -4319,13 +4280,13 @@
         <v>82</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>82</v>
@@ -4333,14 +4294,14 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -4359,19 +4320,19 @@
         <v>94</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>82</v>
@@ -4420,7 +4381,7 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4429,25 +4390,25 @@
         <v>93</v>
       </c>
       <c r="AI19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ19" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ19" t="s" s="2">
-        <v>171</v>
-      </c>
       <c r="AK19" t="s" s="2">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>82</v>
@@ -4455,14 +4416,14 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4481,19 +4442,19 @@
         <v>94</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>82</v>
@@ -4542,7 +4503,7 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4551,25 +4512,25 @@
         <v>93</v>
       </c>
       <c r="AI20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ20" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK20" t="s" s="2">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>82</v>
@@ -4577,10 +4538,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4603,16 +4564,16 @@
         <v>94</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4662,7 +4623,7 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4671,11 +4632,11 @@
         <v>93</v>
       </c>
       <c r="AI21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ21" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ21" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK21" t="s" s="2">
         <v>82</v>
       </c>
@@ -4683,13 +4644,13 @@
         <v>82</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>82</v>
@@ -4697,10 +4658,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4723,19 +4684,17 @@
         <v>94</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>169</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>82</v>
@@ -4784,7 +4743,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4793,25 +4752,25 @@
         <v>81</v>
       </c>
       <c r="AI22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ22" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ22" t="s" s="2">
-        <v>171</v>
-      </c>
       <c r="AK22" t="s" s="2">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>82</v>
@@ -4819,10 +4778,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4845,19 +4804,19 @@
         <v>94</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>82</v>
@@ -4906,7 +4865,7 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4915,36 +4874,36 @@
         <v>93</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>289</v>
+        <v>281</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4967,13 +4926,13 @@
         <v>82</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -5024,7 +4983,7 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -5048,7 +5007,7 @@
         <v>82</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>114</v>
+        <v>287</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>82</v>
@@ -5059,14 +5018,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -5085,16 +5044,16 @@
         <v>82</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="N25" t="s" s="2">
         <v>142</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>144</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -5132,19 +5091,19 @@
         <v>82</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>145</v>
+        <v>290</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>146</v>
+        <v>291</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>147</v>
+        <v>292</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -5153,10 +5112,10 @@
         <v>81</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>82</v>
@@ -5168,7 +5127,7 @@
         <v>82</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>107</v>
+        <v>287</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>82</v>
@@ -5179,10 +5138,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5205,19 +5164,19 @@
         <v>94</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="O26" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="L26" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>303</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -5266,7 +5225,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5275,11 +5234,11 @@
         <v>93</v>
       </c>
       <c r="AI26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ26" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ26" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK26" t="s" s="2">
         <v>82</v>
       </c>
@@ -5287,10 +5246,10 @@
         <v>82</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>82</v>
@@ -5301,10 +5260,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5327,70 +5286,68 @@
         <v>94</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="N27" s="2"/>
+      <c r="O27" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="P27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q27" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="R27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X27" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="Y27" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="Z27" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="N27" t="s" s="2">
+      <c r="AA27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF27" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="P27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q27" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="R27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X27" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="Z27" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="AA27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF27" t="s" s="2">
-        <v>315</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5399,11 +5356,11 @@
         <v>93</v>
       </c>
       <c r="AI27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ27" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ27" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK27" t="s" s="2">
         <v>82</v>
       </c>
@@ -5411,10 +5368,10 @@
         <v>82</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>82</v>
@@ -5425,10 +5382,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5451,19 +5408,17 @@
         <v>94</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>310</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>82</v>
@@ -5473,7 +5428,7 @@
         <v>82</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="T28" t="s" s="2">
         <v>82</v>
@@ -5512,7 +5467,7 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5521,11 +5476,11 @@
         <v>93</v>
       </c>
       <c r="AI28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ28" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK28" t="s" s="2">
         <v>82</v>
       </c>
@@ -5533,10 +5488,10 @@
         <v>82</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>82</v>
@@ -5547,10 +5502,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5573,19 +5528,17 @@
         <v>94</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>329</v>
-      </c>
+        <v>323</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" t="s" s="2">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>82</v>
@@ -5595,7 +5548,7 @@
         <v>82</v>
       </c>
       <c r="S29" t="s" s="2">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="T29" t="s" s="2">
         <v>82</v>
@@ -5634,7 +5587,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5643,10 +5596,10 @@
         <v>93</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>82</v>
@@ -5655,10 +5608,10 @@
         <v>82</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>82</v>
@@ -5669,10 +5622,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5695,19 +5648,19 @@
         <v>94</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>82</v>
@@ -5717,7 +5670,7 @@
         <v>82</v>
       </c>
       <c r="S30" t="s" s="2">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="T30" t="s" s="2">
         <v>82</v>
@@ -5756,7 +5709,7 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5765,11 +5718,11 @@
         <v>93</v>
       </c>
       <c r="AI30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ30" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK30" t="s" s="2">
         <v>82</v>
       </c>
@@ -5777,10 +5730,10 @@
         <v>82</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>82</v>
@@ -5791,10 +5744,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5817,19 +5770,19 @@
         <v>82</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>82</v>
@@ -5854,13 +5807,13 @@
         <v>82</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>82</v>
@@ -5878,7 +5831,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5887,10 +5840,10 @@
         <v>93</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>82</v>
@@ -5899,10 +5852,10 @@
         <v>82</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>82</v>
@@ -5913,10 +5866,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5939,13 +5892,13 @@
         <v>82</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5996,7 +5949,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -6020,7 +5973,7 @@
         <v>82</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>114</v>
+        <v>287</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>82</v>
@@ -6031,14 +5984,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -6057,16 +6010,16 @@
         <v>82</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="N33" t="s" s="2">
         <v>142</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>144</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -6104,19 +6057,19 @@
         <v>82</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>145</v>
+        <v>290</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>146</v>
+        <v>291</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>147</v>
+        <v>292</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6125,10 +6078,10 @@
         <v>81</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>82</v>
@@ -6140,7 +6093,7 @@
         <v>82</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>107</v>
+        <v>287</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>82</v>
@@ -6151,10 +6104,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6177,19 +6130,19 @@
         <v>94</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -6238,7 +6191,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6247,11 +6200,11 @@
         <v>81</v>
       </c>
       <c r="AI34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ34" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK34" t="s" s="2">
         <v>82</v>
       </c>
@@ -6259,10 +6212,10 @@
         <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>82</v>
@@ -6273,10 +6226,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6299,13 +6252,13 @@
         <v>82</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6356,7 +6309,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6380,7 +6333,7 @@
         <v>82</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>114</v>
+        <v>287</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
@@ -6391,14 +6344,14 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -6417,16 +6370,16 @@
         <v>82</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="M36" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="N36" t="s" s="2">
         <v>142</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>144</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6464,19 +6417,19 @@
         <v>82</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>145</v>
+        <v>290</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>146</v>
+        <v>291</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>147</v>
+        <v>292</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6485,10 +6438,10 @@
         <v>81</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>82</v>
@@ -6500,7 +6453,7 @@
         <v>82</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>107</v>
+        <v>287</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
@@ -6511,10 +6464,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6537,19 +6490,19 @@
         <v>94</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>82</v>
@@ -6598,7 +6551,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6607,11 +6560,11 @@
         <v>93</v>
       </c>
       <c r="AI37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ37" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK37" t="s" s="2">
         <v>82</v>
       </c>
@@ -6619,10 +6572,10 @@
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
@@ -6633,10 +6586,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6659,16 +6612,16 @@
         <v>94</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6718,7 +6671,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6727,11 +6680,11 @@
         <v>93</v>
       </c>
       <c r="AI38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ38" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK38" t="s" s="2">
         <v>82</v>
       </c>
@@ -6739,10 +6692,10 @@
         <v>82</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
@@ -6753,10 +6706,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6779,19 +6732,17 @@
         <v>94</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>310</v>
-      </c>
+        <v>376</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -6840,7 +6791,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6849,11 +6800,11 @@
         <v>93</v>
       </c>
       <c r="AI39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ39" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK39" t="s" s="2">
         <v>82</v>
       </c>
@@ -6861,10 +6812,10 @@
         <v>82</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -6875,10 +6826,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6901,19 +6852,17 @@
         <v>94</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>310</v>
-      </c>
+        <v>383</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>82</v>
@@ -6962,7 +6911,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6971,11 +6920,11 @@
         <v>93</v>
       </c>
       <c r="AI40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ40" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK40" t="s" s="2">
         <v>82</v>
       </c>
@@ -6983,10 +6932,10 @@
         <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
@@ -6997,10 +6946,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7023,19 +6972,19 @@
         <v>94</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>82</v>
@@ -7084,7 +7033,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -7093,11 +7042,11 @@
         <v>93</v>
       </c>
       <c r="AI41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ41" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK41" t="s" s="2">
         <v>82</v>
       </c>
@@ -7105,10 +7054,10 @@
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -7119,10 +7068,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7145,19 +7094,19 @@
         <v>94</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -7206,7 +7155,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7215,11 +7164,11 @@
         <v>93</v>
       </c>
       <c r="AI42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ42" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK42" t="s" s="2">
         <v>82</v>
       </c>
@@ -7227,10 +7176,10 @@
         <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
@@ -7241,14 +7190,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7267,19 +7216,19 @@
         <v>82</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -7304,13 +7253,13 @@
         <v>82</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>82</v>
@@ -7328,7 +7277,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7337,36 +7286,36 @@
         <v>81</v>
       </c>
       <c r="AI43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ43" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>422</v>
+        <v>416</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7389,19 +7338,19 @@
         <v>82</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
@@ -7450,7 +7399,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7459,11 +7408,11 @@
         <v>81</v>
       </c>
       <c r="AI44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ44" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK44" t="s" s="2">
         <v>82</v>
       </c>
@@ -7471,10 +7420,10 @@
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -7485,10 +7434,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7511,16 +7460,16 @@
         <v>82</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7546,13 +7495,13 @@
         <v>82</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>82</v>
@@ -7570,7 +7519,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7579,36 +7528,36 @@
         <v>93</v>
       </c>
       <c r="AI45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ45" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>440</v>
+        <v>434</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7631,19 +7580,19 @@
         <v>82</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>82</v>
@@ -7668,13 +7617,13 @@
         <v>82</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>82</v>
@@ -7692,7 +7641,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7701,11 +7650,11 @@
         <v>93</v>
       </c>
       <c r="AI46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ46" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK46" t="s" s="2">
         <v>82</v>
       </c>
@@ -7713,10 +7662,10 @@
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
@@ -7727,10 +7676,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7753,16 +7702,16 @@
         <v>82</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7812,7 +7761,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7821,36 +7770,36 @@
         <v>93</v>
       </c>
       <c r="AI47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ47" t="s" s="2">
-        <v>171</v>
-      </c>
       <c r="AK47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>458</v>
+        <v>452</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7873,16 +7822,16 @@
         <v>82</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7932,7 +7881,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7941,36 +7890,36 @@
         <v>93</v>
       </c>
       <c r="AI48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ48" t="s" s="2">
-        <v>171</v>
-      </c>
       <c r="AK48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>467</v>
+        <v>461</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7993,19 +7942,19 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -8054,7 +8003,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8063,10 +8012,10 @@
         <v>81</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>82</v>
@@ -8075,10 +8024,10 @@
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -8089,10 +8038,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8115,13 +8064,13 @@
         <v>82</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8172,7 +8121,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8196,7 +8145,7 @@
         <v>82</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>114</v>
+        <v>287</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -8207,14 +8156,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -8233,16 +8182,16 @@
         <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="N51" t="s" s="2">
         <v>142</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>144</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8280,19 +8229,19 @@
         <v>82</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>145</v>
+        <v>82</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>146</v>
+        <v>82</v>
       </c>
       <c r="AD51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>147</v>
+        <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8301,10 +8250,10 @@
         <v>81</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>82</v>
@@ -8316,7 +8265,7 @@
         <v>82</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>107</v>
+        <v>287</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8327,14 +8276,14 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -8353,19 +8302,19 @@
         <v>94</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -8414,7 +8363,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8423,10 +8372,10 @@
         <v>81</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>82</v>
@@ -8438,7 +8387,7 @@
         <v>82</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8449,10 +8398,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8475,17 +8424,15 @@
         <v>82</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>488</v>
-      </c>
+        <v>481</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>82</v>
@@ -8534,7 +8481,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8543,10 +8490,10 @@
         <v>93</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>489</v>
+        <v>482</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>490</v>
+        <v>105</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>82</v>
@@ -8555,10 +8502,10 @@
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>492</v>
+        <v>484</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>82</v>
@@ -8569,10 +8516,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>493</v>
+        <v>485</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>493</v>
+        <v>485</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8595,17 +8542,15 @@
         <v>82</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>488</v>
-      </c>
+        <v>487</v>
+      </c>
+      <c r="N54" s="2"/>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>82</v>
@@ -8654,7 +8599,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>493</v>
+        <v>485</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8663,10 +8608,10 @@
         <v>93</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>489</v>
+        <v>482</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>490</v>
+        <v>105</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>82</v>
@@ -8675,10 +8620,10 @@
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>496</v>
+        <v>488</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
@@ -8689,10 +8634,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>497</v>
+        <v>489</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>497</v>
+        <v>489</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8715,19 +8660,19 @@
         <v>82</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>498</v>
+        <v>490</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>499</v>
+        <v>491</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>500</v>
+        <v>492</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>501</v>
+        <v>493</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -8752,13 +8697,13 @@
         <v>82</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>502</v>
+        <v>494</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>503</v>
+        <v>495</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>82</v>
@@ -8776,7 +8721,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>497</v>
+        <v>489</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8785,22 +8730,22 @@
         <v>93</v>
       </c>
       <c r="AI55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ55" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>504</v>
+        <v>496</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>505</v>
+        <v>497</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
@@ -8811,10 +8756,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>506</v>
+        <v>498</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>506</v>
+        <v>498</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8837,19 +8782,19 @@
         <v>82</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>507</v>
+        <v>499</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>508</v>
+        <v>500</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>509</v>
+        <v>501</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>510</v>
+        <v>502</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>82</v>
@@ -8874,13 +8819,13 @@
         <v>82</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>511</v>
+        <v>503</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>512</v>
+        <v>504</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>82</v>
@@ -8898,7 +8843,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>506</v>
+        <v>498</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8907,22 +8852,22 @@
         <v>81</v>
       </c>
       <c r="AI56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ56" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK56" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>504</v>
+        <v>496</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>505</v>
+        <v>497</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
@@ -8933,10 +8878,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>513</v>
+        <v>505</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>513</v>
+        <v>505</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8959,19 +8904,17 @@
         <v>82</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>514</v>
+        <v>506</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>515</v>
+        <v>507</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>517</v>
-      </c>
+        <v>508</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>518</v>
+        <v>509</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>82</v>
@@ -9020,7 +8963,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>513</v>
+        <v>505</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9029,11 +8972,11 @@
         <v>93</v>
       </c>
       <c r="AI57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ57" t="s" s="2">
-        <v>519</v>
-      </c>
       <c r="AK57" t="s" s="2">
         <v>82</v>
       </c>
@@ -9041,10 +8984,10 @@
         <v>82</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>520</v>
+        <v>82</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>521</v>
+        <v>510</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>82</v>
@@ -9055,10 +8998,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>522</v>
+        <v>511</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>522</v>
+        <v>511</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9081,17 +9024,15 @@
         <v>82</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>523</v>
+        <v>512</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>310</v>
-      </c>
+        <v>513</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -9140,7 +9081,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>522</v>
+        <v>511</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9149,11 +9090,11 @@
         <v>93</v>
       </c>
       <c r="AI58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ58" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK58" t="s" s="2">
         <v>82</v>
       </c>
@@ -9161,10 +9102,10 @@
         <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>525</v>
+        <v>514</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
@@ -9175,10 +9116,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>526</v>
+        <v>515</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>526</v>
+        <v>515</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9201,16 +9142,16 @@
         <v>94</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>527</v>
+        <v>516</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>530</v>
+        <v>519</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9260,7 +9201,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>526</v>
+        <v>515</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9269,11 +9210,11 @@
         <v>81</v>
       </c>
       <c r="AI59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ59" t="s" s="2">
-        <v>171</v>
-      </c>
       <c r="AK59" t="s" s="2">
         <v>82</v>
       </c>
@@ -9281,10 +9222,10 @@
         <v>82</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>531</v>
+        <v>520</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>532</v>
+        <v>521</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
@@ -9295,10 +9236,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>533</v>
+        <v>522</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>533</v>
+        <v>522</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9321,16 +9262,16 @@
         <v>94</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>534</v>
+        <v>523</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>535</v>
+        <v>524</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>536</v>
+        <v>525</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>537</v>
+        <v>526</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9380,7 +9321,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>533</v>
+        <v>522</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9389,11 +9330,11 @@
         <v>81</v>
       </c>
       <c r="AI60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ60" t="s" s="2">
-        <v>171</v>
-      </c>
       <c r="AK60" t="s" s="2">
         <v>82</v>
       </c>
@@ -9401,10 +9342,10 @@
         <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>531</v>
+        <v>520</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>538</v>
+        <v>527</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
@@ -9415,10 +9356,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>539</v>
+        <v>528</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>539</v>
+        <v>528</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9441,19 +9382,19 @@
         <v>94</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>540</v>
+        <v>529</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>541</v>
+        <v>530</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>542</v>
+        <v>531</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>543</v>
+        <v>532</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -9502,7 +9443,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>539</v>
+        <v>528</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9511,11 +9452,11 @@
         <v>81</v>
       </c>
       <c r="AI61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ61" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK61" t="s" s="2">
         <v>82</v>
       </c>
@@ -9523,10 +9464,10 @@
         <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>544</v>
+        <v>533</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>545</v>
+        <v>534</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
@@ -9537,10 +9478,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>546</v>
+        <v>535</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>546</v>
+        <v>535</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9563,13 +9504,13 @@
         <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9620,7 +9561,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9644,7 +9585,7 @@
         <v>82</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>114</v>
+        <v>287</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
@@ -9655,14 +9596,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>547</v>
+        <v>536</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>547</v>
+        <v>536</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -9681,16 +9622,16 @@
         <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="N63" t="s" s="2">
         <v>142</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>144</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9728,19 +9669,19 @@
         <v>82</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>145</v>
+        <v>82</v>
       </c>
       <c r="AC63" t="s" s="2">
-        <v>146</v>
+        <v>82</v>
       </c>
       <c r="AD63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>147</v>
+        <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9749,10 +9690,10 @@
         <v>81</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>82</v>
@@ -9764,7 +9705,7 @@
         <v>82</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>107</v>
+        <v>287</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
@@ -9775,14 +9716,14 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>548</v>
+        <v>537</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>548</v>
+        <v>537</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -9801,19 +9742,19 @@
         <v>94</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>82</v>
@@ -9862,7 +9803,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9871,10 +9812,10 @@
         <v>81</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>82</v>
@@ -9886,7 +9827,7 @@
         <v>82</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>82</v>
@@ -9897,10 +9838,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>549</v>
+        <v>538</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>549</v>
+        <v>538</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9923,19 +9864,19 @@
         <v>94</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>550</v>
+        <v>539</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>551</v>
+        <v>540</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>552</v>
+        <v>541</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>82</v>
@@ -9960,13 +9901,13 @@
         <v>82</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>82</v>
@@ -9984,7 +9925,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>549</v>
+        <v>538</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>93</v>
@@ -9993,25 +9934,25 @@
         <v>93</v>
       </c>
       <c r="AI65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ65" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>553</v>
+        <v>542</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>82</v>
@@ -10019,10 +9960,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>554</v>
+        <v>543</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>554</v>
+        <v>543</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10045,19 +9986,19 @@
         <v>94</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>555</v>
+        <v>544</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>556</v>
+        <v>545</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>557</v>
+        <v>546</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>82</v>
@@ -10106,7 +10047,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>554</v>
+        <v>543</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10115,36 +10056,36 @@
         <v>93</v>
       </c>
       <c r="AI66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ66" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>558</v>
+        <v>547</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>289</v>
+        <v>281</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>559</v>
+        <v>548</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>559</v>
+        <v>548</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10167,19 +10108,19 @@
         <v>82</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>560</v>
+        <v>549</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>561</v>
+        <v>550</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>562</v>
+        <v>551</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>82</v>
@@ -10204,13 +10145,13 @@
         <v>82</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>82</v>
@@ -10228,7 +10169,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>559</v>
+        <v>548</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10237,10 +10178,10 @@
         <v>93</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>82</v>
@@ -10249,10 +10190,10 @@
         <v>82</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>82</v>
@@ -10263,14 +10204,14 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>563</v>
+        <v>552</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>563</v>
+        <v>552</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -10289,19 +10230,19 @@
         <v>82</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>82</v>
@@ -10326,13 +10267,13 @@
         <v>82</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>82</v>
@@ -10350,7 +10291,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>563</v>
+        <v>552</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10359,36 +10300,36 @@
         <v>81</v>
       </c>
       <c r="AI68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AJ68" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AK68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>422</v>
+        <v>416</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>564</v>
+        <v>553</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>564</v>
+        <v>553</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10414,16 +10355,16 @@
         <v>83</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>565</v>
+        <v>554</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>566</v>
+        <v>555</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>82</v>
@@ -10472,7 +10413,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>564</v>
+        <v>553</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10484,7 +10425,7 @@
         <v>82</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>82</v>
@@ -10493,10 +10434,10 @@
         <v>82</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-04T08:19:08+00:00</t>
+    <t>2025-03-27T13:15:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-27T13:15:18+00:00</t>
+    <t>2025-03-27T14:27:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-27T14:27:05+00:00</t>
+    <t>2025-03-27T15:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-27T15:41:15+00:00</t>
+    <t>2025-03-27T15:45:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
@@ -45,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Cholestérol total</t>
+    <t>Cholestérol - total</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-27T15:45:03+00:00</t>
+    <t>2025-03-27T15:47:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-27T15:47:29+00:00</t>
+    <t>2025-03-31T07:44:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Profil de la ressource Observation pour définir le cholestérol total</t>
+    <t>Profil biologie de la ressource Observation pour définir le cholestérol total</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T07:44:46+00:00</t>
+    <t>2025-03-31T07:48:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T07:48:14+00:00</t>
+    <t>2025-03-31T07:48:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T07:48:39+00:00</t>
+    <t>2025-03-31T11:47:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T11:47:14+00:00</t>
+    <t>2025-03-31T11:46:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T11:46:38+00:00</t>
+    <t>2025-03-31T14:05:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T14:05:37+00:00</t>
+    <t>2025-03-31T15:50:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T15:50:51+00:00</t>
+    <t>2025-03-31T15:55:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T15:55:12+00:00</t>
+    <t>2025-03-31T16:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T16:04:27+00:00</t>
+    <t>2025-03-31T16:16:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T16:16:40+00:00</t>
+    <t>2025-03-31T16:26:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T16:26:20+00:00</t>
+    <t>2025-03-31T16:37:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T16:37:23+00:00</t>
+    <t>2025-04-01T07:11:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-01T07:11:22+00:00</t>
+    <t>2025-04-01T07:12:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-01T07:12:21+00:00</t>
+    <t>2025-04-01T07:12:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-02T12:26:08+00:00</t>
+    <t>2025-07-07T09:50:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-07T09:50:30+00:00</t>
+    <t>2025-12-23T16:18:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -383,7 +383,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -519,7 +519,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|DeviceRequest|ImmunizationRecommendation|MedicationRequest|NutritionOrder|ServiceRequest)
+    <t xml:space="preserve">Reference(CarePlan|4.0.1|DeviceRequest|4.0.1|ImmunizationRecommendation|4.0.1|MedicationRequest|4.0.1|NutritionOrder|4.0.1|ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -548,7 +548,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|MedicationDispense|MedicationStatement|Procedure|Immunization|ImagingStudy)
+    <t xml:space="preserve">Reference(MedicationAdministration|4.0.1|MedicationDispense|4.0.1|MedicationStatement|4.0.1|Procedure|4.0.1|Immunization|4.0.1|ImagingStudy|4.0.1)
 </t>
   </si>
   <si>
@@ -631,7 +631,7 @@
     <t>Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
@@ -674,7 +674,7 @@
     <t>Codes identifying names of simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -698,7 +698,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Group|Device|Location)
+    <t xml:space="preserve">Reference(Patient|4.0.1|Group|4.0.1|Device|4.0.1|Location|4.0.1)
 </t>
   </si>
   <si>
@@ -729,7 +729,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -752,7 +752,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(Encounter|4.0.1)
 </t>
   </si>
   <si>
@@ -843,7 +843,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|CareTeam|Patient|RelatedPerson)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|CareTeam|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1)
 </t>
   </si>
   <si>
@@ -1091,7 +1091,7 @@
     <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">obs-6
@@ -1302,7 +1302,7 @@
     <t>Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1358,7 +1358,7 @@
     <t>Codes describing anatomical locations. May include laterality.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1400,7 +1400,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(Specimen|4.0.1)
 </t>
   </si>
   <si>
@@ -1428,7 +1428,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric)
+    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
 </t>
   </si>
   <si>
@@ -1508,7 +1508,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1558,7 +1558,7 @@
     <t>Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -1591,7 +1591,7 @@
     <t>Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
@@ -1628,7 +1628,7 @@
     <t>Observation.hasMember</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Observation|QuestionnaireResponse|MolecularSequence)
+    <t xml:space="preserve">Reference(Observation|4.0.1|QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1)
 </t>
   </si>
   <si>
@@ -1650,7 +1650,7 @@
     <t>Observation.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DocumentReference|ImagingStudy|Media|QuestionnaireResponse|Observation|MolecularSequence)
+    <t xml:space="preserve">Reference(DocumentReference|4.0.1|ImagingStudy|4.0.1|Media|4.0.1|QuestionnaireResponse|4.0.1|Observation|4.0.1|MolecularSequence|4.0.1)
 </t>
   </si>
   <si>
@@ -2080,7 +2080,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="95.26171875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="122.43359375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -7909,7 +7909,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
         <v>461</v>
       </c>
@@ -10443,12 +10443,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AP69">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-23T16:18:55+00:00</t>
+    <t>2026-01-06T09:57:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-06T09:57:05+00:00</t>
+    <t>2026-01-06T10:01:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-06T10:01:17+00:00</t>
+    <t>2026-01-19T08:51:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$80</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2683" uniqueCount="555">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3098" uniqueCount="609">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T08:51:58+00:00</t>
+    <t>2026-01-19T09:23:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -342,13 +342,190 @@
 </t>
   </si>
   <si>
-    <t>Observation.implicitRules</t>
+    <t>Observation.meta.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Observation.meta.extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>Observation.meta.versionId</t>
+  </si>
+  <si>
+    <t>Version specific identifier</t>
+  </si>
+  <si>
+    <t>The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
+  </si>
+  <si>
+    <t>The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
+  </si>
+  <si>
+    <t>Meta.versionId</t>
+  </si>
+  <si>
+    <t>Observation.meta.lastUpdated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instant
+</t>
+  </si>
+  <si>
+    <t>When the resource version last changed</t>
+  </si>
+  <si>
+    <t>When the resource last changed - e.g. when the version changed.</t>
+  </si>
+  <si>
+    <t>This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4/http.html#read) interaction.</t>
+  </si>
+  <si>
+    <t>Meta.lastUpdated</t>
+  </si>
+  <si>
+    <t>Observation.meta.source</t>
   </si>
   <si>
     <t xml:space="preserve">uri
 </t>
   </si>
   <si>
+    <t>Uri identifiant les systèmes tiers ayant envoyé la ressource. L’uri est sous la forme d’une oid : « urn:oid:xx.xx.xx »</t>
+  </si>
+  <si>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+  </si>
+  <si>
+    <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
+This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
+  </si>
+  <si>
+    <t>Meta.source</t>
+  </si>
+  <si>
+    <t>Observation.meta.profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Profiles this resource claims to conform to</t>
+  </si>
+  <si>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
+  </si>
+  <si>
+    <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
+  </si>
+  <si>
+    <t>Meta.profile</t>
+  </si>
+  <si>
+    <t>Observation.meta.security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Security Labels applied to this resource</t>
+  </si>
+  <si>
+    <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
+  </si>
+  <si>
+    <t>The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
+  </si>
+  <si>
+    <t>Meta.security</t>
+  </si>
+  <si>
+    <t>Observation.meta.tag</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
+  </si>
+  <si>
+    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
+  </si>
+  <si>
+    <t>Meta.tag</t>
+  </si>
+  <si>
+    <t>Observation.implicitRules</t>
+  </si>
+  <si>
     <t>A set of rules under which this content was created</t>
   </si>
   <si>
@@ -444,28 +621,66 @@
     <t>Observation.extension</t>
   </si>
   <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>Observation.extension:supportingInfo</t>
+  </si>
+  <si>
+    <t>supportingInfo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {workflow-supportingInfo}
 </t>
   </si>
   <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+    <t>Other information that may be relevant to this event.</t>
+  </si>
+  <si>
+    <t>Autres ressources pertinentes *du dossier patient*</t>
+  </si>
+  <si>
+    <t>Observation.extension:MesReasonForMeasurement</t>
+  </si>
+  <si>
+    <t>MesReasonForMeasurement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-reason-for-measurement}
+</t>
+  </si>
+  <si>
+    <t>Motif de la mesure</t>
+  </si>
+  <si>
+    <t>Motif de la mesure
+Texte libre (ex. diabète, surpoids, hypercholestérolémie, risque cardiovasculaire, suivi, ...)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>Observation.extension:MesOriginOfData</t>
+  </si>
+  <si>
+    <t>MesOriginOfData</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-origin-of-data}
+</t>
+  </si>
+  <si>
+    <t>Valeur d'origine de la donnée. Cette extension est présente uniquement si le résultat contenu dans Observation.value provient d'une conversion (par ex. g/L converti en mmol/L)</t>
+  </si>
+  <si>
+    <t>Extension pour tracer l'origine de la donnée issue d'un compte rendu de biologie (CR-Bio).</t>
   </si>
   <si>
     <t>Observation.modifierExtension</t>
@@ -668,9 +883,6 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>example</t>
-  </si>
-  <si>
     <t>Codes identifying names of simple observations.</t>
   </si>
   <si>
@@ -698,7 +910,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|4.0.1|Group|4.0.1|Device|4.0.1|Location|4.0.1)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient)
 </t>
   </si>
   <si>
@@ -752,7 +964,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter|4.0.1)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-encounter)
 </t>
   </si>
   <si>
@@ -818,10 +1030,6 @@
     <t>Observation.issued</t>
   </si>
   <si>
-    <t xml:space="preserve">instant
-</t>
-  </si>
-  <si>
     <t>Date/Time this version was made available</t>
   </si>
   <si>
@@ -843,7 +1051,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|CareTeam|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1)
+    <t xml:space="preserve">Reference(CareTeam|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-related-person|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|PractitionerRole|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization)
 </t>
   </si>
   <si>
@@ -906,39 +1114,7 @@
     <t>Observation.value[x].id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Observation.value[x].extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>Observation.value[x].value</t>
@@ -1085,9 +1261,6 @@
     <t>For many results it is necessary to handle exceptional values in measurements.</t>
   </si>
   <si>
-    <t>extensible</t>
-  </si>
-  <si>
     <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
@@ -1108,10 +1281,6 @@
   </si>
   <si>
     <t>Observation.dataAbsentReason.coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
   </si>
   <si>
     <t>Code defined by a terminology system</t>
@@ -2067,12 +2236,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP69"/>
+  <dimension ref="A1:AP80"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="42.26953125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="42.26953125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="23.171875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -2080,7 +2249,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="122.43359375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="232.12890625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2094,7 +2263,7 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="54.6171875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="51.64453125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
@@ -2621,10 +2790,10 @@
         <v>82</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K5" t="s" s="2">
         <v>107</v>
@@ -2635,9 +2804,7 @@
       <c r="M5" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="N5" t="s" s="2">
-        <v>110</v>
-      </c>
+      <c r="N5" s="2"/>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
         <v>82</v>
@@ -2686,7 +2853,7 @@
         <v>82</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>80</v>
@@ -2698,7 +2865,7 @@
         <v>82</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>82</v>
@@ -2710,7 +2877,7 @@
         <v>82</v>
       </c>
       <c r="AN5" t="s" s="2">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="AO5" t="s" s="2">
         <v>82</v>
@@ -2728,14 +2895,14 @@
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>82</v>
@@ -2747,16 +2914,16 @@
         <v>82</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2782,43 +2949,43 @@
         <v>82</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="Y6" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z6" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA6" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB6" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="Z6" t="s" s="2">
+      <c r="AC6" t="s" s="2">
         <v>119</v>
       </c>
-      <c r="AA6" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AD6" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>82</v>
@@ -2830,7 +2997,7 @@
         <v>82</v>
       </c>
       <c r="AN6" t="s" s="2">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="AO6" t="s" s="2">
         <v>82</v>
@@ -2841,14 +3008,14 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -2864,10 +3031,10 @@
         <v>82</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>123</v>
+        <v>95</v>
       </c>
       <c r="L7" t="s" s="2">
         <v>124</v>
@@ -2950,7 +3117,7 @@
         <v>82</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>128</v>
+        <v>82</v>
       </c>
       <c r="AO7" t="s" s="2">
         <v>82</v>
@@ -2961,21 +3128,21 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>130</v>
+        <v>82</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>82</v>
@@ -2984,19 +3151,19 @@
         <v>82</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="L8" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="M8" t="s" s="2">
         <v>131</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="M8" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>134</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -3046,19 +3213,19 @@
         <v>82</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>82</v>
@@ -3070,7 +3237,7 @@
         <v>82</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="AO8" t="s" s="2">
         <v>82</v>
@@ -3081,21 +3248,21 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>82</v>
@@ -3104,19 +3271,19 @@
         <v>82</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -3166,19 +3333,19 @@
         <v>82</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>82</v>
@@ -3190,7 +3357,7 @@
         <v>82</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="AO9" t="s" s="2">
         <v>82</v>
@@ -3201,14 +3368,14 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -3221,26 +3388,24 @@
         <v>82</v>
       </c>
       <c r="I10" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J10" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="J10" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K10" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>148</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>82</v>
       </c>
@@ -3288,7 +3453,7 @@
         <v>82</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -3300,7 +3465,7 @@
         <v>82</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>82</v>
@@ -3312,7 +3477,7 @@
         <v>82</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="AO10" t="s" s="2">
         <v>82</v>
@@ -3323,10 +3488,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3349,18 +3514,18 @@
         <v>94</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="N11" s="2"/>
-      <c r="O11" t="s" s="2">
-        <v>154</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="N11" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>82</v>
       </c>
@@ -3384,13 +3549,13 @@
         <v>82</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>82</v>
+        <v>151</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>82</v>
+        <v>152</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>82</v>
+        <v>153</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>82</v>
@@ -3408,7 +3573,7 @@
         <v>82</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -3423,19 +3588,19 @@
         <v>105</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>156</v>
+        <v>82</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>158</v>
+        <v>82</v>
       </c>
       <c r="AP11" t="s" s="2">
         <v>82</v>
@@ -3443,14 +3608,14 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>160</v>
+        <v>82</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -3469,18 +3634,18 @@
         <v>94</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N12" s="2"/>
-      <c r="O12" t="s" s="2">
-        <v>164</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>82</v>
       </c>
@@ -3504,13 +3669,13 @@
         <v>82</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>82</v>
+        <v>159</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>82</v>
+        <v>160</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>82</v>
+        <v>161</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>82</v>
@@ -3528,7 +3693,7 @@
         <v>82</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -3543,16 +3708,16 @@
         <v>105</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>166</v>
+        <v>82</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>167</v>
+        <v>82</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>82</v>
@@ -3563,42 +3728,42 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>169</v>
+        <v>82</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J13" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>170</v>
+        <v>135</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3648,13 +3813,13 @@
         <v>82</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>82</v>
@@ -3663,16 +3828,16 @@
         <v>105</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>174</v>
+        <v>82</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>175</v>
+        <v>82</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>176</v>
+        <v>82</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>82</v>
@@ -3683,10 +3848,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3694,7 +3859,7 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>93</v>
@@ -3703,26 +3868,24 @@
         <v>82</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>113</v>
+        <v>169</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>181</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>82</v>
       </c>
@@ -3746,13 +3909,13 @@
         <v>82</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>82</v>
@@ -3770,10 +3933,10 @@
         <v>82</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH14" t="s" s="2">
         <v>93</v>
@@ -3785,19 +3948,19 @@
         <v>105</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>185</v>
+        <v>82</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>186</v>
+        <v>82</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>187</v>
+        <v>82</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>188</v>
+        <v>82</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>189</v>
+        <v>82</v>
       </c>
       <c r="AP14" t="s" s="2">
         <v>82</v>
@@ -3805,21 +3968,21 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>82</v>
+        <v>178</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>82</v>
@@ -3831,20 +3994,18 @@
         <v>82</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>195</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>82</v>
       </c>
@@ -3868,13 +4029,13 @@
         <v>82</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>196</v>
+        <v>82</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>197</v>
+        <v>82</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>82</v>
@@ -3892,13 +4053,13 @@
         <v>82</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>82</v>
@@ -3916,10 +4077,10 @@
         <v>82</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>199</v>
+        <v>82</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>82</v>
@@ -3927,21 +4088,21 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>82</v>
@@ -3950,23 +4111,21 @@
         <v>82</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>202</v>
+        <v>188</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>203</v>
+        <v>189</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>205</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>82</v>
       </c>
@@ -3975,7 +4134,7 @@
         <v>82</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>206</v>
+        <v>82</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>82</v>
@@ -3990,13 +4149,13 @@
         <v>82</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>207</v>
+        <v>82</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>208</v>
+        <v>82</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>209</v>
+        <v>82</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>82</v>
@@ -4014,45 +4173,45 @@
         <v>82</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>210</v>
+        <v>82</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>211</v>
+        <v>82</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>212</v>
+        <v>82</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>213</v>
+        <v>192</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>214</v>
+        <v>82</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>215</v>
+        <v>82</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>216</v>
+        <v>193</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>216</v>
+        <v>193</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4063,7 +4222,7 @@
         <v>80</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>82</v>
@@ -4072,23 +4231,19 @@
         <v>82</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>217</v>
+        <v>114</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>221</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>82</v>
       </c>
@@ -4124,46 +4279,44 @@
         <v>82</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="AC17" s="2"/>
       <c r="AD17" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>216</v>
+        <v>196</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>222</v>
+        <v>82</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>223</v>
+        <v>82</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>224</v>
+        <v>82</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>225</v>
+        <v>82</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>82</v>
@@ -4171,12 +4324,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>226</v>
+        <v>197</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="C18" s="2"/>
+        <v>193</v>
+      </c>
+      <c r="C18" t="s" s="2">
+        <v>198</v>
+      </c>
       <c r="D18" t="s" s="2">
         <v>82</v>
       </c>
@@ -4185,7 +4340,7 @@
         <v>80</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>82</v>
@@ -4194,20 +4349,18 @@
         <v>82</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>227</v>
+        <v>199</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>228</v>
+        <v>200</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>230</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>82</v>
@@ -4256,7 +4409,7 @@
         <v>82</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>226</v>
+        <v>196</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4268,7 +4421,7 @@
         <v>82</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>82</v>
@@ -4277,13 +4430,13 @@
         <v>82</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>212</v>
+        <v>82</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>231</v>
+        <v>82</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>225</v>
+        <v>82</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>82</v>
@@ -4291,14 +4444,16 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>232</v>
+        <v>202</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="C19" s="2"/>
+        <v>193</v>
+      </c>
+      <c r="C19" t="s" s="2">
+        <v>203</v>
+      </c>
       <c r="D19" t="s" s="2">
-        <v>233</v>
+        <v>82</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -4314,23 +4469,19 @@
         <v>82</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>234</v>
+        <v>204</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>235</v>
+        <v>205</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>238</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>82</v>
       </c>
@@ -4378,34 +4529,34 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>82</v>
+        <v>207</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>239</v>
+        <v>82</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>240</v>
+        <v>82</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>241</v>
+        <v>82</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>242</v>
+        <v>82</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>82</v>
@@ -4413,14 +4564,16 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>243</v>
+        <v>208</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="C20" s="2"/>
+        <v>193</v>
+      </c>
+      <c r="C20" t="s" s="2">
+        <v>209</v>
+      </c>
       <c r="D20" t="s" s="2">
-        <v>244</v>
+        <v>82</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4436,23 +4589,19 @@
         <v>82</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>245</v>
+        <v>210</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>246</v>
+        <v>211</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>249</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>82</v>
       </c>
@@ -4500,34 +4649,34 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>243</v>
+        <v>196</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>82</v>
+        <v>207</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>250</v>
+        <v>82</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>251</v>
+        <v>82</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>252</v>
+        <v>82</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>253</v>
+        <v>82</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>82</v>
@@ -4535,44 +4684,46 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>254</v>
+        <v>213</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>254</v>
+        <v>213</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>255</v>
+        <v>114</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>256</v>
+        <v>214</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>257</v>
+        <v>215</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="O21" s="2"/>
+        <v>117</v>
+      </c>
+      <c r="O21" t="s" s="2">
+        <v>216</v>
+      </c>
       <c r="P21" t="s" s="2">
         <v>82</v>
       </c>
@@ -4620,19 +4771,19 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>254</v>
+        <v>217</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>82</v>
@@ -4641,13 +4792,13 @@
         <v>82</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>259</v>
+        <v>82</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>260</v>
+        <v>192</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>261</v>
+        <v>82</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>82</v>
@@ -4655,10 +4806,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>262</v>
+        <v>218</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>262</v>
+        <v>218</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4681,17 +4832,17 @@
         <v>94</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>263</v>
+        <v>219</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>264</v>
+        <v>220</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>265</v>
+        <v>221</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>266</v>
+        <v>222</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>82</v>
@@ -4740,7 +4891,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>262</v>
+        <v>218</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4755,19 +4906,19 @@
         <v>105</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>267</v>
+        <v>223</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>268</v>
+        <v>224</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>269</v>
+        <v>225</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>270</v>
+        <v>226</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>82</v>
@@ -4775,21 +4926,21 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>271</v>
+        <v>227</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>271</v>
+        <v>227</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>82</v>
+        <v>228</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>82</v>
@@ -4801,19 +4952,17 @@
         <v>94</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>272</v>
+        <v>229</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>273</v>
+        <v>230</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>275</v>
-      </c>
+        <v>231</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>276</v>
+        <v>232</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>82</v>
@@ -4862,56 +5011,56 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>271</v>
+        <v>227</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>277</v>
+        <v>82</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>82</v>
+        <v>233</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>278</v>
+        <v>82</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>279</v>
+        <v>234</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>280</v>
+        <v>235</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>281</v>
+        <v>82</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>282</v>
+        <v>236</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>282</v>
+        <v>236</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>82</v>
+        <v>237</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>82</v>
@@ -4920,18 +5069,20 @@
         <v>82</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>283</v>
+        <v>238</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>284</v>
+        <v>239</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="N24" s="2"/>
+        <v>240</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>241</v>
+      </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>82</v>
@@ -4980,31 +5131,31 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>286</v>
+        <v>236</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>82</v>
+        <v>242</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>82</v>
+        <v>243</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>287</v>
+        <v>244</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>82</v>
@@ -5015,44 +5166,46 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>288</v>
+        <v>245</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>288</v>
+        <v>245</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>139</v>
+        <v>169</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>140</v>
+        <v>246</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>289</v>
+        <v>247</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O25" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="O25" t="s" s="2">
+        <v>249</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
       </c>
@@ -5076,58 +5229,58 @@
         <v>82</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>82</v>
+        <v>250</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>82</v>
+        <v>251</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>82</v>
+        <v>252</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>290</v>
+        <v>82</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>291</v>
+        <v>82</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>292</v>
+        <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>293</v>
+        <v>245</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>82</v>
+        <v>253</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>82</v>
+        <v>254</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>82</v>
+        <v>255</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>287</v>
+        <v>256</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>82</v>
+        <v>257</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>82</v>
@@ -5135,10 +5288,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>294</v>
+        <v>258</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>294</v>
+        <v>258</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5146,10 +5299,10 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>82</v>
@@ -5158,22 +5311,22 @@
         <v>82</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>295</v>
+        <v>259</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>296</v>
+        <v>260</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>297</v>
+        <v>261</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>298</v>
+        <v>262</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>299</v>
+        <v>263</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -5198,13 +5351,13 @@
         <v>82</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>82</v>
+        <v>173</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>82</v>
+        <v>264</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>82</v>
+        <v>265</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>82</v>
@@ -5222,13 +5375,13 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>300</v>
+        <v>258</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>82</v>
@@ -5243,13 +5396,13 @@
         <v>82</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>301</v>
+        <v>82</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>302</v>
+        <v>266</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>82</v>
+        <v>267</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>82</v>
@@ -5257,18 +5410,18 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>303</v>
+        <v>268</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>303</v>
+        <v>268</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>82</v>
+        <v>269</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>93</v>
@@ -5277,35 +5430,35 @@
         <v>82</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J27" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>113</v>
+        <v>259</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>304</v>
+        <v>270</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>271</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>272</v>
+      </c>
       <c r="O27" t="s" s="2">
-        <v>306</v>
+        <v>273</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q27" t="s" s="2">
-        <v>307</v>
-      </c>
+      <c r="Q27" s="2"/>
       <c r="R27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="S27" t="s" s="2">
-        <v>82</v>
+        <v>274</v>
       </c>
       <c r="T27" t="s" s="2">
         <v>82</v>
@@ -5320,13 +5473,13 @@
         <v>82</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>182</v>
+        <v>159</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>308</v>
+        <v>275</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>309</v>
+        <v>276</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>82</v>
@@ -5344,10 +5497,10 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>310</v>
+        <v>268</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH27" t="s" s="2">
         <v>93</v>
@@ -5359,30 +5512,30 @@
         <v>105</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>82</v>
+        <v>277</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>82</v>
+        <v>278</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>311</v>
+        <v>279</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>312</v>
+        <v>280</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>82</v>
+        <v>281</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>82</v>
+        <v>282</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>313</v>
+        <v>283</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>313</v>
+        <v>283</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5390,7 +5543,7 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>93</v>
@@ -5405,17 +5558,19 @@
         <v>94</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>314</v>
+        <v>285</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>286</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>287</v>
+      </c>
       <c r="O28" t="s" s="2">
-        <v>316</v>
+        <v>288</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>82</v>
@@ -5425,7 +5580,7 @@
         <v>82</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>317</v>
+        <v>82</v>
       </c>
       <c r="T28" t="s" s="2">
         <v>82</v>
@@ -5464,7 +5619,7 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>318</v>
+        <v>283</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5479,19 +5634,19 @@
         <v>105</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>82</v>
+        <v>289</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>319</v>
+        <v>290</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>320</v>
+        <v>291</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>82</v>
+        <v>292</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>82</v>
@@ -5499,10 +5654,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>321</v>
+        <v>293</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>321</v>
+        <v>293</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5513,7 +5668,7 @@
         <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>82</v>
@@ -5525,18 +5680,18 @@
         <v>94</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>107</v>
+        <v>294</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>322</v>
+        <v>295</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="N29" s="2"/>
-      <c r="O29" t="s" s="2">
-        <v>324</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>82</v>
       </c>
@@ -5545,7 +5700,7 @@
         <v>82</v>
       </c>
       <c r="S29" t="s" s="2">
-        <v>325</v>
+        <v>82</v>
       </c>
       <c r="T29" t="s" s="2">
         <v>82</v>
@@ -5584,16 +5739,16 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>326</v>
+        <v>293</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>327</v>
+        <v>82</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>105</v>
@@ -5605,13 +5760,13 @@
         <v>82</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>319</v>
+        <v>279</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>328</v>
+        <v>298</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>82</v>
+        <v>292</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>82</v>
@@ -5619,18 +5774,18 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>329</v>
+        <v>299</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>329</v>
+        <v>299</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>82</v>
+        <v>300</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>93</v>
@@ -5645,19 +5800,19 @@
         <v>94</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>113</v>
+        <v>301</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>330</v>
+        <v>302</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>331</v>
+        <v>303</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>332</v>
+        <v>304</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>333</v>
+        <v>305</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>82</v>
@@ -5667,7 +5822,7 @@
         <v>82</v>
       </c>
       <c r="S30" t="s" s="2">
-        <v>317</v>
+        <v>82</v>
       </c>
       <c r="T30" t="s" s="2">
         <v>82</v>
@@ -5706,7 +5861,7 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>334</v>
+        <v>299</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5721,19 +5876,19 @@
         <v>105</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>82</v>
+        <v>306</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>319</v>
+        <v>307</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>335</v>
+        <v>308</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>82</v>
+        <v>309</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>82</v>
@@ -5741,14 +5896,14 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>336</v>
+        <v>310</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>336</v>
+        <v>310</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>82</v>
+        <v>311</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5764,22 +5919,22 @@
         <v>82</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>191</v>
+        <v>312</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>337</v>
+        <v>313</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>338</v>
+        <v>314</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>339</v>
+        <v>315</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>340</v>
+        <v>316</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>82</v>
@@ -5804,13 +5959,13 @@
         <v>82</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>341</v>
+        <v>82</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>342</v>
+        <v>82</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>343</v>
+        <v>82</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>82</v>
@@ -5828,7 +5983,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>336</v>
+        <v>310</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5837,25 +5992,25 @@
         <v>93</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>344</v>
+        <v>82</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>82</v>
+        <v>317</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>136</v>
+        <v>318</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>345</v>
+        <v>319</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>82</v>
+        <v>320</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>82</v>
@@ -5863,10 +6018,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>346</v>
+        <v>321</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>346</v>
+        <v>321</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5886,18 +6041,20 @@
         <v>82</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>283</v>
+        <v>129</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>284</v>
+        <v>322</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>323</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>324</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>82</v>
@@ -5946,7 +6103,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>286</v>
+        <v>321</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5958,7 +6115,7 @@
         <v>82</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>82</v>
@@ -5967,13 +6124,13 @@
         <v>82</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>82</v>
+        <v>325</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>287</v>
+        <v>326</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>82</v>
+        <v>327</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>82</v>
@@ -5981,14 +6138,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>347</v>
+        <v>328</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>347</v>
+        <v>328</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -6004,21 +6161,21 @@
         <v>82</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>139</v>
+        <v>329</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>140</v>
+        <v>330</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O33" s="2"/>
+        <v>331</v>
+      </c>
+      <c r="N33" s="2"/>
+      <c r="O33" t="s" s="2">
+        <v>332</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
       </c>
@@ -6054,19 +6211,19 @@
         <v>82</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>290</v>
+        <v>82</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>291</v>
+        <v>82</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>292</v>
+        <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>293</v>
+        <v>328</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6078,22 +6235,22 @@
         <v>82</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>82</v>
+        <v>333</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>82</v>
+        <v>334</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>287</v>
+        <v>335</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>82</v>
+        <v>336</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>82</v>
@@ -6101,10 +6258,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>348</v>
+        <v>337</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>348</v>
+        <v>337</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6115,7 +6272,7 @@
         <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>82</v>
@@ -6127,19 +6284,19 @@
         <v>94</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>349</v>
+        <v>338</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>350</v>
+        <v>339</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>351</v>
+        <v>340</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>352</v>
+        <v>341</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>353</v>
+        <v>342</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -6188,16 +6345,16 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>354</v>
+        <v>337</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>82</v>
+        <v>343</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>105</v>
@@ -6206,27 +6363,27 @@
         <v>82</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>82</v>
+        <v>344</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>82</v>
+        <v>347</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6249,13 +6406,13 @@
         <v>82</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>283</v>
+        <v>107</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>284</v>
+        <v>108</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>285</v>
+        <v>109</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6306,7 +6463,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>286</v>
+        <v>110</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6330,7 +6487,7 @@
         <v>82</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>287</v>
+        <v>111</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
@@ -6341,14 +6498,14 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>138</v>
+        <v>113</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -6367,16 +6524,16 @@
         <v>82</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>139</v>
+        <v>114</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>140</v>
+        <v>115</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>289</v>
+        <v>116</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>142</v>
+        <v>117</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6414,19 +6571,19 @@
         <v>82</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>290</v>
+        <v>118</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>291</v>
+        <v>119</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>292</v>
+        <v>120</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>293</v>
+        <v>121</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6438,7 +6595,7 @@
         <v>82</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>144</v>
+        <v>122</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>82</v>
@@ -6450,7 +6607,7 @@
         <v>82</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>287</v>
+        <v>111</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
@@ -6461,10 +6618,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6487,19 +6644,19 @@
         <v>94</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>107</v>
+        <v>351</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>82</v>
@@ -6548,7 +6705,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6569,10 +6726,10 @@
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
@@ -6583,10 +6740,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6603,28 +6760,30 @@
         <v>82</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J38" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>283</v>
+        <v>169</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="O38" s="2"/>
+        <v>361</v>
+      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" t="s" s="2">
+        <v>362</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q38" s="2"/>
+      <c r="Q38" t="s" s="2">
+        <v>363</v>
+      </c>
       <c r="R38" t="s" s="2">
         <v>82</v>
       </c>
@@ -6644,13 +6803,13 @@
         <v>82</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>82</v>
+        <v>250</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>82</v>
+        <v>364</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>82</v>
+        <v>365</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>82</v>
@@ -6668,7 +6827,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6689,10 +6848,10 @@
         <v>82</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
@@ -6703,10 +6862,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6729,17 +6888,17 @@
         <v>94</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -6749,7 +6908,7 @@
         <v>82</v>
       </c>
       <c r="S39" t="s" s="2">
-        <v>82</v>
+        <v>373</v>
       </c>
       <c r="T39" t="s" s="2">
         <v>82</v>
@@ -6788,7 +6947,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6809,10 +6968,10 @@
         <v>82</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -6823,10 +6982,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6849,17 +7008,17 @@
         <v>94</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>283</v>
+        <v>135</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>82</v>
@@ -6869,7 +7028,7 @@
         <v>82</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>82</v>
+        <v>381</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>82</v>
@@ -6908,7 +7067,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6917,7 +7076,7 @@
         <v>93</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>82</v>
+        <v>383</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>105</v>
@@ -6929,10 +7088,10 @@
         <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>386</v>
+        <v>375</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
@@ -6943,10 +7102,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6954,7 +7113,7 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>93</v>
@@ -6969,19 +7128,19 @@
         <v>94</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="O41" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="L41" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>393</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>82</v>
@@ -6991,7 +7150,7 @@
         <v>82</v>
       </c>
       <c r="S41" t="s" s="2">
-        <v>82</v>
+        <v>373</v>
       </c>
       <c r="T41" t="s" s="2">
         <v>82</v>
@@ -7030,7 +7189,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -7051,10 +7210,10 @@
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>395</v>
+        <v>375</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -7065,10 +7224,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7088,22 +7247,22 @@
         <v>82</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>283</v>
+        <v>259</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -7128,13 +7287,13 @@
         <v>82</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>82</v>
+        <v>151</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>82</v>
+        <v>397</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>82</v>
+        <v>398</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>82</v>
@@ -7152,7 +7311,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>402</v>
+        <v>392</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7161,7 +7320,7 @@
         <v>93</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>82</v>
+        <v>399</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>105</v>
@@ -7173,10 +7332,10 @@
         <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>403</v>
+        <v>192</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
@@ -7187,21 +7346,21 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>406</v>
+        <v>82</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>82</v>
@@ -7213,20 +7372,16 @@
         <v>82</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>191</v>
+        <v>107</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>407</v>
+        <v>108</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>410</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N43" s="2"/>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>82</v>
       </c>
@@ -7250,13 +7405,13 @@
         <v>82</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>341</v>
+        <v>82</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>411</v>
+        <v>82</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>412</v>
+        <v>82</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>82</v>
@@ -7274,49 +7429,49 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>405</v>
+        <v>110</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>413</v>
+        <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>414</v>
+        <v>82</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>415</v>
+        <v>111</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>416</v>
+        <v>82</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>417</v>
+        <v>402</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>417</v>
+        <v>402</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7335,20 +7490,18 @@
         <v>82</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>418</v>
+        <v>114</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>419</v>
+        <v>115</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>420</v>
+        <v>116</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>422</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>82</v>
       </c>
@@ -7384,19 +7537,19 @@
         <v>82</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>417</v>
+        <v>121</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7408,7 +7561,7 @@
         <v>82</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>82</v>
@@ -7417,10 +7570,10 @@
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>423</v>
+        <v>82</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>424</v>
+        <v>111</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -7431,10 +7584,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>425</v>
+        <v>403</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>425</v>
+        <v>403</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7445,7 +7598,7 @@
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>82</v>
@@ -7454,21 +7607,23 @@
         <v>82</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>191</v>
+        <v>147</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>426</v>
+        <v>404</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>427</v>
+        <v>405</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="O45" s="2"/>
+        <v>406</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>407</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>82</v>
       </c>
@@ -7492,13 +7647,13 @@
         <v>82</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>207</v>
+        <v>82</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>429</v>
+        <v>82</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>430</v>
+        <v>82</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>82</v>
@@ -7516,13 +7671,13 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>425</v>
+        <v>408</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>82</v>
@@ -7534,27 +7689,27 @@
         <v>82</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>431</v>
+        <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>432</v>
+        <v>409</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>433</v>
+        <v>410</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>434</v>
+        <v>82</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>435</v>
+        <v>411</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>435</v>
+        <v>411</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7562,7 +7717,7 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>93</v>
@@ -7577,20 +7732,16 @@
         <v>82</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>191</v>
+        <v>107</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>436</v>
+        <v>108</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>439</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>82</v>
       </c>
@@ -7614,11 +7765,13 @@
         <v>82</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="Y46" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z46" t="s" s="2">
-        <v>440</v>
+        <v>82</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>82</v>
@@ -7636,7 +7789,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>435</v>
+        <v>110</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7648,7 +7801,7 @@
         <v>82</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>82</v>
@@ -7657,10 +7810,10 @@
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>441</v>
+        <v>82</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>442</v>
+        <v>111</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
@@ -7671,21 +7824,21 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>443</v>
+        <v>412</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>443</v>
+        <v>412</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>82</v>
@@ -7697,16 +7850,16 @@
         <v>82</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>444</v>
+        <v>114</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>445</v>
+        <v>115</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>446</v>
+        <v>116</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>447</v>
+        <v>117</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7744,57 +7897,57 @@
         <v>82</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>443</v>
+        <v>121</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>448</v>
+        <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>449</v>
+        <v>82</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>450</v>
+        <v>111</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>451</v>
+        <v>82</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>452</v>
+        <v>413</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>452</v>
+        <v>413</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7802,7 +7955,7 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>93</v>
@@ -7814,21 +7967,23 @@
         <v>82</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>453</v>
+        <v>135</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>454</v>
+        <v>414</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>455</v>
+        <v>415</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="O48" s="2"/>
+        <v>416</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>417</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
       </c>
@@ -7876,7 +8031,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>452</v>
+        <v>418</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7894,27 +8049,27 @@
         <v>82</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>457</v>
+        <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>458</v>
+        <v>419</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>459</v>
+        <v>420</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>460</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>461</v>
+        <v>421</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>461</v>
+        <v>421</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7922,35 +8077,33 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J49" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="I49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J49" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K49" t="s" s="2">
-        <v>462</v>
+        <v>107</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>463</v>
+        <v>422</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>464</v>
+        <v>423</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>466</v>
-      </c>
+        <v>424</v>
+      </c>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>82</v>
       </c>
@@ -7998,19 +8151,19 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>461</v>
+        <v>425</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>467</v>
+        <v>105</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>82</v>
@@ -8019,10 +8172,10 @@
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>468</v>
+        <v>426</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>469</v>
+        <v>427</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -8033,10 +8186,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>470</v>
+        <v>428</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>470</v>
+        <v>428</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8044,7 +8197,7 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>93</v>
@@ -8056,19 +8209,21 @@
         <v>82</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>283</v>
+        <v>169</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>284</v>
+        <v>429</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>285</v>
+        <v>430</v>
       </c>
       <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
+      <c r="O50" t="s" s="2">
+        <v>431</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
       </c>
@@ -8116,7 +8271,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>286</v>
+        <v>432</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8128,7 +8283,7 @@
         <v>82</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>82</v>
@@ -8137,10 +8292,10 @@
         <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>82</v>
+        <v>433</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>287</v>
+        <v>434</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -8151,21 +8306,21 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>471</v>
+        <v>435</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>471</v>
+        <v>435</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>82</v>
@@ -8174,21 +8329,21 @@
         <v>82</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>139</v>
+        <v>107</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>140</v>
+        <v>436</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O51" s="2"/>
+        <v>437</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" t="s" s="2">
+        <v>438</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
       </c>
@@ -8236,19 +8391,19 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>293</v>
+        <v>439</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>82</v>
@@ -8257,10 +8412,10 @@
         <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>82</v>
+        <v>440</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>287</v>
+        <v>441</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8271,45 +8426,45 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>472</v>
+        <v>442</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>472</v>
+        <v>442</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>473</v>
+        <v>82</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J52" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>139</v>
+        <v>443</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>474</v>
+        <v>444</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>475</v>
+        <v>445</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>142</v>
+        <v>446</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>148</v>
+        <v>447</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -8358,19 +8513,19 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>476</v>
+        <v>448</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>82</v>
@@ -8379,10 +8534,10 @@
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>82</v>
+        <v>449</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>136</v>
+        <v>450</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8393,10 +8548,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>477</v>
+        <v>451</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>477</v>
+        <v>451</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8416,19 +8571,23 @@
         <v>82</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>478</v>
+        <v>107</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>479</v>
+        <v>452</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
+        <v>453</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>455</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>82</v>
       </c>
@@ -8476,7 +8635,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>477</v>
+        <v>456</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8485,7 +8644,7 @@
         <v>93</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>481</v>
+        <v>82</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>105</v>
@@ -8497,10 +8656,10 @@
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>482</v>
+        <v>457</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>483</v>
+        <v>458</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>82</v>
@@ -8511,21 +8670,21 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>484</v>
+        <v>459</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>484</v>
+        <v>459</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>82</v>
+        <v>460</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>82</v>
@@ -8537,16 +8696,20 @@
         <v>82</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>478</v>
+        <v>259</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>485</v>
+        <v>461</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
+        <v>462</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>464</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
       </c>
@@ -8570,13 +8733,13 @@
         <v>82</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>82</v>
+        <v>151</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>82</v>
+        <v>465</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>82</v>
+        <v>466</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>82</v>
@@ -8594,16 +8757,16 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>484</v>
+        <v>459</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>481</v>
+        <v>82</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>105</v>
@@ -8612,27 +8775,27 @@
         <v>82</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>82</v>
+        <v>467</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>482</v>
+        <v>468</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>487</v>
+        <v>469</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>82</v>
+        <v>470</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>488</v>
+        <v>471</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>488</v>
+        <v>471</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8643,7 +8806,7 @@
         <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>82</v>
@@ -8655,19 +8818,19 @@
         <v>82</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>191</v>
+        <v>472</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>489</v>
+        <v>473</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>490</v>
+        <v>474</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>491</v>
+        <v>475</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>492</v>
+        <v>476</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -8692,13 +8855,13 @@
         <v>82</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>493</v>
+        <v>82</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>494</v>
+        <v>82</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>82</v>
@@ -8716,13 +8879,13 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>488</v>
+        <v>471</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>82</v>
@@ -8734,13 +8897,13 @@
         <v>82</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>495</v>
+        <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>496</v>
+        <v>477</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>415</v>
+        <v>478</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
@@ -8751,10 +8914,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>497</v>
+        <v>479</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>497</v>
+        <v>479</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8765,7 +8928,7 @@
         <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>82</v>
@@ -8777,20 +8940,18 @@
         <v>82</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>191</v>
+        <v>259</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>498</v>
+        <v>480</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>499</v>
+        <v>481</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>501</v>
-      </c>
+        <v>482</v>
+      </c>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>82</v>
       </c>
@@ -8814,13 +8975,13 @@
         <v>82</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>207</v>
+        <v>159</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>502</v>
+        <v>483</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>503</v>
+        <v>484</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>82</v>
@@ -8838,13 +8999,13 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>497</v>
+        <v>479</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>82</v>
@@ -8856,27 +9017,27 @@
         <v>82</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>495</v>
+        <v>485</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>496</v>
+        <v>486</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>415</v>
+        <v>487</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>82</v>
+        <v>488</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>504</v>
+        <v>489</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>504</v>
+        <v>489</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8884,10 +9045,10 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>82</v>
@@ -8899,17 +9060,19 @@
         <v>82</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>505</v>
+        <v>259</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>506</v>
+        <v>490</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="N57" s="2"/>
+        <v>491</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>492</v>
+      </c>
       <c r="O57" t="s" s="2">
-        <v>508</v>
+        <v>493</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>82</v>
@@ -8934,13 +9097,11 @@
         <v>82</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y57" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
-        <v>82</v>
+        <v>494</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>82</v>
@@ -8958,7 +9119,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>504</v>
+        <v>489</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8979,10 +9140,10 @@
         <v>82</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>82</v>
+        <v>495</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>509</v>
+        <v>496</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>82</v>
@@ -8993,10 +9154,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>510</v>
+        <v>497</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>510</v>
+        <v>497</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9019,15 +9180,17 @@
         <v>82</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>283</v>
+        <v>498</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>511</v>
+        <v>499</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>500</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>501</v>
+      </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -9076,7 +9239,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>510</v>
+        <v>497</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9094,27 +9257,27 @@
         <v>82</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>82</v>
+        <v>502</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>482</v>
+        <v>503</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>82</v>
+        <v>505</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>514</v>
+        <v>506</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>514</v>
+        <v>506</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9125,7 +9288,7 @@
         <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>82</v>
@@ -9134,19 +9297,19 @@
         <v>82</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>515</v>
+        <v>507</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>516</v>
+        <v>508</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>517</v>
+        <v>509</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>518</v>
+        <v>510</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9196,13 +9359,13 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>514</v>
+        <v>506</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>82</v>
@@ -9214,27 +9377,27 @@
         <v>82</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>82</v>
+        <v>511</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>82</v>
+        <v>514</v>
       </c>
     </row>
-    <row r="60" hidden="true">
+    <row r="60">
       <c r="A60" t="s" s="2">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9242,33 +9405,35 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="O60" s="2"/>
+        <v>519</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>520</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
       </c>
@@ -9316,7 +9481,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9328,7 +9493,7 @@
         <v>82</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>105</v>
+        <v>521</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>82</v>
@@ -9337,10 +9502,10 @@
         <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
@@ -9351,10 +9516,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9365,7 +9530,7 @@
         <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>82</v>
@@ -9374,23 +9539,19 @@
         <v>82</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>462</v>
+        <v>107</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>528</v>
+        <v>108</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>531</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>82</v>
       </c>
@@ -9438,19 +9599,19 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>527</v>
+        <v>110</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>82</v>
@@ -9459,10 +9620,10 @@
         <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>532</v>
+        <v>82</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>533</v>
+        <v>111</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
@@ -9473,21 +9634,21 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>534</v>
+        <v>525</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>534</v>
+        <v>525</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>82</v>
@@ -9499,15 +9660,17 @@
         <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>283</v>
+        <v>114</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>284</v>
+        <v>115</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="N62" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>82</v>
@@ -9556,19 +9719,19 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>286</v>
+        <v>121</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>82</v>
@@ -9580,7 +9743,7 @@
         <v>82</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>287</v>
+        <v>111</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
@@ -9591,14 +9754,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>535</v>
+        <v>526</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>535</v>
+        <v>526</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>138</v>
+        <v>527</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -9611,24 +9774,26 @@
         <v>82</v>
       </c>
       <c r="I63" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>139</v>
+        <v>114</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>140</v>
+        <v>528</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>289</v>
+        <v>529</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O63" s="2"/>
+        <v>117</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>216</v>
+      </c>
       <c r="P63" t="s" s="2">
         <v>82</v>
       </c>
@@ -9676,7 +9841,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>293</v>
+        <v>530</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9688,7 +9853,7 @@
         <v>82</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>144</v>
+        <v>122</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>82</v>
@@ -9700,7 +9865,7 @@
         <v>82</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>287</v>
+        <v>192</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
@@ -9711,46 +9876,42 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>473</v>
+        <v>82</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I64" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>139</v>
+        <v>532</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>474</v>
+        <v>533</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>148</v>
-      </c>
+        <v>534</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>82</v>
       </c>
@@ -9798,19 +9959,19 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>476</v>
+        <v>531</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>82</v>
+        <v>535</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>82</v>
@@ -9819,10 +9980,10 @@
         <v>82</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>82</v>
+        <v>536</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>136</v>
+        <v>537</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>82</v>
@@ -9833,10 +9994,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9856,23 +10017,19 @@
         <v>82</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>191</v>
+        <v>532</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="N65" t="s" s="2">
         <v>540</v>
       </c>
-      <c r="O65" t="s" s="2">
-        <v>205</v>
-      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>82</v>
       </c>
@@ -9896,13 +10053,13 @@
         <v>82</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>207</v>
+        <v>82</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>208</v>
+        <v>82</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>209</v>
+        <v>82</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>82</v>
@@ -9920,16 +10077,16 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH65" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>82</v>
+        <v>535</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>105</v>
@@ -9938,16 +10095,16 @@
         <v>82</v>
       </c>
       <c r="AL65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="AN65" t="s" s="2">
         <v>541</v>
       </c>
-      <c r="AM65" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>213</v>
-      </c>
       <c r="AO65" t="s" s="2">
-        <v>214</v>
+        <v>82</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>82</v>
@@ -9969,7 +10126,7 @@
         <v>80</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>82</v>
@@ -9978,22 +10135,22 @@
         <v>82</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="L66" t="s" s="2">
         <v>543</v>
       </c>
-      <c r="L66" t="s" s="2">
+      <c r="M66" t="s" s="2">
         <v>544</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="N66" t="s" s="2">
         <v>545</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>276</v>
+        <v>546</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>82</v>
@@ -10018,13 +10175,13 @@
         <v>82</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>82</v>
+        <v>173</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>82</v>
+        <v>547</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>82</v>
+        <v>548</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>82</v>
@@ -10060,27 +10217,27 @@
         <v>82</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>279</v>
+        <v>550</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>280</v>
+        <v>469</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>281</v>
+        <v>82</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10091,7 +10248,7 @@
         <v>80</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>82</v>
@@ -10103,19 +10260,19 @@
         <v>82</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>191</v>
+        <v>259</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>340</v>
+        <v>555</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>82</v>
@@ -10140,13 +10297,13 @@
         <v>82</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>341</v>
+        <v>159</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>342</v>
+        <v>556</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>343</v>
+        <v>557</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>82</v>
@@ -10164,16 +10321,16 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>344</v>
+        <v>82</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>105</v>
@@ -10182,13 +10339,13 @@
         <v>82</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>82</v>
+        <v>549</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>136</v>
+        <v>550</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>345</v>
+        <v>469</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>82</v>
@@ -10199,21 +10356,21 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>406</v>
+        <v>82</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>82</v>
@@ -10225,19 +10382,17 @@
         <v>82</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>191</v>
+        <v>559</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>407</v>
+        <v>560</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>409</v>
-      </c>
+        <v>561</v>
+      </c>
+      <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>410</v>
+        <v>562</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>82</v>
@@ -10262,13 +10417,13 @@
         <v>82</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>341</v>
+        <v>82</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>411</v>
+        <v>82</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>412</v>
+        <v>82</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>82</v>
@@ -10286,13 +10441,13 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>82</v>
@@ -10304,27 +10459,27 @@
         <v>82</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>413</v>
+        <v>82</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>414</v>
+        <v>82</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>415</v>
+        <v>563</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>416</v>
+        <v>82</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>552</v>
+        <v>564</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>552</v>
+        <v>564</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10335,7 +10490,7 @@
         <v>80</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>82</v>
@@ -10347,20 +10502,16 @@
         <v>82</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>553</v>
+        <v>565</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>466</v>
-      </c>
+        <v>566</v>
+      </c>
+      <c r="N69" s="2"/>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>82</v>
       </c>
@@ -10408,13 +10559,13 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>552</v>
+        <v>564</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>82</v>
@@ -10429,20 +10580,1352 @@
         <v>82</v>
       </c>
       <c r="AM69" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="AO69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP69" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="70" hidden="true">
+      <c r="A70" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="O70" s="2"/>
+      <c r="P70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="AO70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP70" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="71" hidden="true">
+      <c r="A71" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="O71" s="2"/>
+      <c r="P71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="AO71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP71" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="72" hidden="true">
+      <c r="A72" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="O72" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="P72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="AO72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP72" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="73" hidden="true">
+      <c r="A73" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="N73" s="2"/>
+      <c r="O73" s="2"/>
+      <c r="P73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AO73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP73" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="74" hidden="true">
+      <c r="A74" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O74" s="2"/>
+      <c r="P74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AO74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP74" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="75" hidden="true">
+      <c r="A75" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O75" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="P75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AO75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP75" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="76" hidden="true">
+      <c r="A76" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="P76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q76" s="2"/>
+      <c r="R76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AO76" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AP76" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="77" hidden="true">
+      <c r="A77" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="O77" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="P77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q77" s="2"/>
+      <c r="R77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="AN77" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="AO77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP77" t="s" s="2">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="78" hidden="true">
+      <c r="A78" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="C78" s="2"/>
+      <c r="D78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E78" s="2"/>
+      <c r="F78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G78" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K78" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="O78" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="P78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q78" s="2"/>
+      <c r="R78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF78" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="AG78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH78" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI78" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AN78" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="AO78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP78" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="79" hidden="true">
+      <c r="A79" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="C79" s="2"/>
+      <c r="D79" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="E79" s="2"/>
+      <c r="F79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K79" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="O79" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="P79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q79" s="2"/>
+      <c r="R79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X79" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="Z79" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF79" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="AG79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="AM79" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="AN69" t="s" s="2">
+      <c r="AN79" t="s" s="2">
         <v>469</v>
       </c>
-      <c r="AO69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP69" t="s" s="2">
+      <c r="AO79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP79" t="s" s="2">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="80" hidden="true">
+      <c r="A80" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="C80" s="2"/>
+      <c r="D80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E80" s="2"/>
+      <c r="F80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K80" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="O80" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="P80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q80" s="2"/>
+      <c r="R80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF80" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="AG80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ80" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM80" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="AN80" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="AO80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP80" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP69">
+  <autoFilter ref="A1:AP80">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -10452,7 +11935,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI68">
+  <conditionalFormatting sqref="A2:AI79">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:23:14+00:00</t>
+    <t>2026-01-19T09:39:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:39:10+00:00</t>
+    <t>2026-01-19T09:47:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:47:31+00:00</t>
+    <t>2026-01-19T09:54:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1545,7 +1545,7 @@
     <t>Observation.method</t>
   </si>
   <si>
-    <t>How it was done</t>
+    <t>La méthode de mesure du cholestérol total est obligatoire pour déterminer si des résultats sont comparables et ainsi utiliser cette donnée.</t>
   </si>
   <si>
     <t>Indicates the mechanism used to perform the observation.</t>
@@ -1557,7 +1557,7 @@
     <t>In some cases, method can impact results and is thus used for determining whether results can be compared or determining significance of results.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/1.2.250.1.213.1.1.5.789</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-technique-biologie-cisis</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -2264,7 +2264,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="51.64453125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="54.12109375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:54:18+00:00</t>
+    <t>2026-01-19T09:56:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:56:13+00:00</t>
+    <t>2026-01-19T10:07:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T10:07:50+00:00</t>
+    <t>2026-01-20T07:44:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1545,7 +1545,7 @@
     <t>Observation.method</t>
   </si>
   <si>
-    <t>La méthode de mesure du cholestérol total est obligatoire pour déterminer si des résultats sont comparables et ainsi utiliser cette donnée.</t>
+    <t>La méthode de mesure du cholestérol total est fortement conseillée pour déterminer si des résultats sont comparables et ainsi utiliser cette donnée.</t>
   </si>
   <si>
     <t>Indicates the mechanism used to perform the observation.</t>
@@ -9032,7 +9032,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="57" hidden="true">
+    <row r="57">
       <c r="A57" t="s" s="2">
         <v>489</v>
       </c>
@@ -9045,13 +9045,13 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>82</v>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T07:44:39+00:00</t>
+    <t>2026-01-20T09:11:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -9405,10 +9405,10 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>94</v>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T09:11:57+00:00</t>
+    <t>2026-01-20T09:43:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T09:43:53+00:00</t>
+    <t>2026-01-20T09:47:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T09:47:48+00:00</t>
+    <t>2026-01-20T10:06:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T10:06:11+00:00</t>
+    <t>2026-01-20T11:11:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -9408,7 +9408,7 @@
         <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>94</v>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-observation-cholesterol-total.xlsx
@@ -39,7 +39,7 @@
     <t>Name</t>
   </si>
   <si>
-    <t>MesFrObservationCholesterolTotal</t>
+    <t>MesObservationCholesterolTotal</t>
   </si>
   <si>
     <t>Title</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T11:11:06+00:00</t>
+    <t>2026-01-20T12:50:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -667,20 +667,21 @@
 </t>
   </si>
   <si>
-    <t>Observation.extension:MesOriginOfData</t>
-  </si>
-  <si>
-    <t>MesOriginOfData</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-origin-of-data}
+    <t>Observation.extension:mes-original-data</t>
+  </si>
+  <si>
+    <t>mes-original-data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-original-data}
 </t>
   </si>
   <si>
     <t>Valeur d'origine de la donnée. Cette extension est présente uniquement si le résultat contenu dans Observation.value provient d'une conversion (par ex. g/L converti en mmol/L)</t>
   </si>
   <si>
-    <t>Extension pour tracer l'origine de la donnée issue d'un compte rendu de biologie (CR-Bio).</t>
+    <t>Extension permettant de renseigner la donnée originale. 
+Dans le cas où une conversion d'unité a été effectuée sur la valeur de la mesure, cette extension permet de conserver la valeur originale telle que mesurée par le dispositif.</t>
   </si>
   <si>
     <t>Observation.modifierExtension</t>
